--- a/data/obx_xlsx/AKRBP.OL.xlsx
+++ b/data/obx_xlsx/AKRBP.OL.xlsx
@@ -12825,7 +12825,9 @@
         <f t="shared" si="2"/>
         <v>354.03</v>
       </c>
-      <c r="U69" s="15"/>
+      <c r="U69" s="17">
+        <v>63.0</v>
+      </c>
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
